--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-001_オンライン設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-001_オンライン設計書.xlsx
@@ -32,8 +32,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ONL-020" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ONL-021" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ONL-022" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通部品一覧" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通基盤への追加改修" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ONL-023" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通部品一覧" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通基盤への追加改修" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -357,10 +358,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6962775" cy="8267700"/>
+    <ext cx="8572500" cy="12392025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -374,9 +375,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -732,7 +730,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -763,6 +761,8 @@
       </c>
       <c r="D12" s="9" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -960,7 +960,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -1167,7 +1166,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
@@ -1338,7 +1336,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -1545,7 +1542,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
@@ -1740,7 +1736,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -1935,7 +1930,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -2106,7 +2100,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -2289,7 +2282,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -2460,7 +2452,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -2631,7 +2622,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -2651,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2779,6 +2769,29 @@
         </is>
       </c>
       <c r="E5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>ONL-001 をログイン堅牢化（正規化・失敗回数・30分ロック・E-017・mustChangePassword・JWT 2時間・401/403 JSON）に合わせて改訂。ONL-023（パスワード変更）を追加し、処理一覧・共通部品一覧（BootstrapAdminInitializer / ChangePasswordRequest ほか）・共通基盤への追加改修（users 4列・Flyway）を更新</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2943,7 +2956,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3114,7 +3126,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3273,7 +3284,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -3432,7 +3442,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -3543,7 +3552,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
@@ -3773,7 +3781,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
@@ -3788,6 +3795,225 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>処理ID/名</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>ONL-023 パスワード変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>機能ID</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password（API-023）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>認可</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>全員（認証必須。本人のパスワードのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>処理手順1</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ログイン中のトークンから本人のユーザーIDを取得（リクエストでユーザーを指定させない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>処理手順2</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>現在のパスワードと新しいパスワードを検証（必須・新パスワードは72文字以内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>処理手順3</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>ユーザーを取得（存在しない=E-015）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>処理手順4</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>現在のパスワードを BCrypt で照合（不一致=E-018。ロック用の失敗回数は加算しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>処理手順5</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>新しいパスワードのポリシー検査：12文字以上／英字と数字を両方含む／現在のパスワードと異なる（違反=E-002）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>処理手順6</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>password_hash を更新し、must_change_password=false、password_changed_at=現在日時（JST）に更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>処理手順7</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>レスポンス HTTP 204（本文なし）。発行済みトークンは失効しない（有効期限 2 時間まで有効）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>使用テーブル</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>users: R/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>E-001, E-002, E-015, E-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>トランザクション</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>更新を伴う処理は1つのトランザクション（@Transactional）で行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>▶ 実装レベルの詳細（クラス・メソッド・処理詳細・SQL・テスト観点）は KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx（フォルダ: 03_詳細設計/01_オンライン設計）を参照。本シートは概要。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3871,7 +4097,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>ClockConfig</t>
+          <t>BootstrapAdminInitializer</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -3881,29 +4107,29 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>CommandLineRunner</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>java.time.Clock Bean（Asia/Tokyo）。時刻取得を差し替え可能にしてテスト容易にする</t>
+          <t>本番の初期管理者（ADMIN）1名の作成。@Order(2)。users が空かつ bootstrap 設定が揃うときのみ。パスワードがポリシー違反なら起動失敗（fail-fast）</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>ONL-013, ONL-016, ONL-017</t>
+          <t>ONL-023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>ClockConfig / AppTime</t>
+          <t>ClockConfig</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -3913,29 +4139,29 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Configuration / Utility</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Clock Bean（Asia/Tokyo）／toIso()</t>
+          <t>java.time.Clock Bean（Asia/Tokyo）。時刻取得を差し替え可能にしてテスト容易にする</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>ONL-003, ONL-004, ONL-009, ONL-010, ONL-019</t>
+          <t>ONL-013, ONL-016, ONL-017</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>DevDataInitializer</t>
+          <t>ClockConfig / AppTime</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -3945,25 +4171,29 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>CommandLineRunner</t>
+          <t>Configuration / Utility</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>開発用テストユーザー投入（本番では無効）</t>
+          <t>Clock Bean（Asia/Tokyo）／toIso()</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="n"/>
+          <t>ONL-001 実装済</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>ONL-003, ONL-004, ONL-009, ONL-010, ONL-019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SecurityConfig</t>
+          <t>DevDataInitializer</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -3973,12 +4203,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>CommandLineRunner</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義</t>
+          <t>開発用ダミーユーザー100名（ADMIN/MANAGER/EMPLOYEE。実在しない架空データ）の投入。@Order(1)。users が空かつ seed-password 設定時のみ。本番では使わない</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -3986,44 +4216,44 @@
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>ONL-002, ONL-009, ONL-014, ONL-015, ONL-016, ONL-017, ONL-018, ONL-020</t>
-        </is>
-      </c>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>AdminHolidayController</t>
+          <t>SecurityConfig</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>controller</t>
+          <t>config</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>API-016 の 3 操作の受付</t>
+          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義。401（E-001）/ 403（E-010）の JSON 応答（authenticationEntryPoint / accessDeniedHandler）を含む</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>ONL-016</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="n"/>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>ONL-002, ONL-009, ONL-014, ONL-015, ONL-016, ONL-017, ONL-018, ONL-020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>AdminLeaveGrantController</t>
+          <t>AdminHolidayController</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -4038,12 +4268,12 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>GET/POST/PUT の受付・Service 呼出・応答返却（管理者限定）</t>
+          <t>API-016 の 3 操作の受付</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
@@ -4051,7 +4281,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>AdminLeaveTypeController</t>
+          <t>AdminLeaveGrantController</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -4066,12 +4296,12 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>API-015 の 4 操作の受付</t>
+          <t>GET/POST/PUT の受付・Service 呼出・応答返却（管理者限定）</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="F9" s="10" t="n"/>
@@ -4079,7 +4309,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>AdminReportController</t>
+          <t>AdminLeaveTypeController</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -4094,12 +4324,12 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>リクエスト受付・format による JSON／CSV の切替・応答ヘッダ設定</t>
+          <t>API-015 の 4 操作の受付</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="F10" s="10" t="n"/>
@@ -4107,7 +4337,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>AdminUserController</t>
+          <t>AdminReportController</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -4122,12 +4352,12 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>API-014 の 5 操作の受付・ログインユーザーID の取り出し</t>
+          <t>リクエスト受付・format による JSON／CSV の切替・応答ヘッダ設定</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="F11" s="10" t="n"/>
@@ -4135,7 +4365,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>ApprovalController</t>
+          <t>AdminUserController</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -4150,24 +4380,20 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>承認系 API の入口（API-009〜012）。本処理で pending を実装（クラスは先に着手した処理が新規作成）</t>
+          <t>API-014 の 5 操作の受付・ログインユーザーID の取り出し</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>ONL-009</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>ONL-010, ONL-011, ONL-012</t>
-        </is>
-      </c>
+          <t>ONL-014</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>AttendanceController</t>
+          <t>ApprovalController</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -4182,24 +4408,24 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>打刻・月次勤怠の API 入口（本処理で clockIn を定義。ONL-003 が clockOut、ONL-004 が getMonthly を追加）</t>
+          <t>承認系 API の入口（API-009〜012）。本処理で pending を実装（クラスは先に着手した処理が新規作成）</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>ONL-003, ONL-004</t>
+          <t>ONL-010, ONL-011, ONL-012</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>AuthController</t>
+          <t>AttendanceController</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -4214,20 +4440,24 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>リクエスト受付・Service 呼出・応答返却</t>
+          <t>打刻・月次勤怠の API 入口（本処理で clockIn を定義。ONL-003 が clockOut、ONL-004 が getMonthly を追加）</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n"/>
+          <t>ONL-002</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>ONL-003, ONL-004</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LeaveBalanceController</t>
+          <t>AuthController</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4242,20 +4472,24 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>API-013 の受付・本人 ID の取り出し</t>
+          <t>リクエスト受付・Service 呼出・応答返却（login は ONL-001、changePassword は ONL-023 が追加）</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>ONL-013</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n"/>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeController</t>
+          <t>LeaveBalanceController</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -4270,12 +4504,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>API-021 の受付（認証済みなら誰でも可）</t>
+          <t>API-013 の受付・本人 ID の取り出し</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>ONL-021</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="F16" s="10" t="n"/>
@@ -4283,7 +4517,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>ManagerController</t>
+          <t>LeaveTypeController</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -4298,12 +4532,12 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>リクエスト受付・ログインユーザーID の取得・Service 呼出</t>
+          <t>API-021 の受付（認証済みなら誰でも可）</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-021</t>
         </is>
       </c>
       <c r="F17" s="10" t="n"/>
@@ -4311,7 +4545,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>NotificationController</t>
+          <t>ManagerController</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4326,12 +4560,12 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>通知 API の入口（GET 一覧／POST 既読化）</t>
+          <t>リクエスト受付・ログインユーザーID の取得・Service 呼出</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="F18" s="10" t="n"/>
@@ -4339,7 +4573,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>RequestController</t>
+          <t>NotificationController</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -4354,52 +4588,52 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>申請 API（API-005〜008, 022）の入口。本処理は create</t>
+          <t>通知 API の入口（GET 一覧／POST 既読化）</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>ONL-006, ONL-007, ONL-008, ONL-022</t>
-        </is>
-      </c>
+          <t>ONL-019</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>ApprovalCommentRequest</t>
+          <t>RequestController</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>dto</t>
+          <t>controller</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>DTO(record)</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
+          <t>申請 API（API-005〜008, 022）の入口。本処理は create</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="n"/>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>ONL-006, ONL-007, ONL-008, ONL-022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>ApprovalCommentRequest / ApprovalResultResponse</t>
+          <t>ApprovalCommentRequest</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -4414,24 +4648,20 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>リクエスト（comment）／応答（requestStatus）。ONL-010 で定義済みの共用 DTO</t>
+          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>ONL-011, ONL-012</t>
-        </is>
-      </c>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>ApprovalResultResponse</t>
+          <t>ApprovalCommentRequest / ApprovalResultResponse</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -4446,20 +4676,24 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>正常応答（requestStatus）。ONL-011/012 も共用</t>
+          <t>リクエスト（comment）／応答（requestStatus）。ONL-010 で定義済みの共用 DTO</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="n"/>
+          <t>ONL-001 実装済</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>ONL-011, ONL-012</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>AttendanceItem</t>
+          <t>ApprovalResultResponse</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -4474,12 +4708,12 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>日別の明細（1日1件）</t>
+          <t>正常応答（requestStatus）。ONL-011/012 も共用</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>ONL-004</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="F23" s="10" t="n"/>
@@ -4487,7 +4721,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>ClockInResponse</t>
+          <t>AttendanceItem</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -4502,12 +4736,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>出勤打刻の正常応答（workDate, clockIn）</t>
+          <t>日別の明細（1日1件）</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-004</t>
         </is>
       </c>
       <c r="F24" s="10" t="n"/>
@@ -4515,7 +4749,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>ClockOutResponse</t>
+          <t>ChangePasswordRequest</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -4530,12 +4764,12 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>退勤打刻の正常応答（clockOut, workMinutes, overtimeMinutes）</t>
+          <t>リクエスト（currentPassword / newPassword）と入力チェック定義（newPassword は72文字以内）</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>ONL-003</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -4543,7 +4777,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>CreateRequestRequest</t>
+          <t>ClockInResponse</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -4558,12 +4792,12 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>リクエスト＋入力チェック定義</t>
+          <t>出勤打刻の正常応答（workDate, clockIn）</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="F26" s="10" t="n"/>
@@ -4571,7 +4805,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>CreateRequestResponse</t>
+          <t>ClockOutResponse</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -4586,12 +4820,12 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>正常応答 {requestId, status}</t>
+          <t>退勤打刻の正常応答（clockOut, workMinutes, overtimeMinutes）</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-003</t>
         </is>
       </c>
       <c r="F27" s="10" t="n"/>
@@ -4599,7 +4833,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>ErrorResponse</t>
+          <t>CreateRequestRequest</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -4614,24 +4848,20 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>共通エラー応答</t>
+          <t>リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>ONL-002, ONL-019, ONL-021</t>
-        </is>
-      </c>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>HolidayDetailResponse</t>
+          <t>CreateRequestResponse</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -4646,12 +4876,12 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>単一応答 {holiday}（登録・削除）</t>
+          <t>正常応答 {requestId, status}</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F29" s="10" t="n"/>
@@ -4659,7 +4889,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>HolidayListResponse</t>
+          <t>ErrorResponse</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -4674,20 +4904,24 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>一覧応答 {year, holidays[]}</t>
+          <t>共通エラー応答</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>ONL-016</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="n"/>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>ONL-002, ONL-019, ONL-021, ONL-023</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>HolidayRequest</t>
+          <t>HolidayDetailResponse</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -4702,7 +4936,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>登録リクエスト＋入力チェック</t>
+          <t>単一応答 {holiday}（登録・削除）</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -4715,7 +4949,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>HolidayResponse</t>
+          <t>HolidayListResponse</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -4730,7 +4964,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>祝日1件の表現</t>
+          <t>一覧応答 {year, holidays[]}</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -4743,7 +4977,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>LeaveBalanceResponse</t>
+          <t>HolidayRequest</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -4758,12 +4992,12 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>正常応答。入れ子 record: Item（種別ごと）/ Grant（付与行ごと）/ Mandatory5（年5日進捗）</t>
+          <t>登録リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="F33" s="10" t="n"/>
@@ -4771,7 +5005,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>LeaveGrantAdjustRequest</t>
+          <t>HolidayResponse</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -4786,12 +5020,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PUT リクエスト＋入力チェック定義</t>
+          <t>祝日1件の表現</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="F34" s="10" t="n"/>
@@ -4799,7 +5033,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>LeaveGrantCreateRequest</t>
+          <t>LeaveBalanceResponse</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -4814,12 +5048,12 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>POST リクエスト＋入力チェック定義</t>
+          <t>正常応答。入れ子 record: Item（種別ごと）/ Grant（付与行ごと）/ Mandatory5（年5日進捗）</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="F35" s="10" t="n"/>
@@ -4827,7 +5061,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>LeaveGrantListResponse</t>
+          <t>LeaveGrantAdjustRequest</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -4842,7 +5076,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>GET 応答（従業員情報＋ grants[]）</t>
+          <t>PUT リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -4855,7 +5089,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>LeaveGrantResponse</t>
+          <t>LeaveGrantCreateRequest</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -4870,7 +5104,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>付与 1 行分の応答（POST/PUT の戻り・GET の要素）</t>
+          <t>POST リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -4883,7 +5117,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>LeaveGrantRow</t>
+          <t>LeaveGrantListResponse</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -4898,7 +5132,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>findGrantRows の戻り型（内部用）</t>
+          <t>GET 応答（従業員情報＋ grants[]）</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -4911,7 +5145,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeDetailResponse</t>
+          <t>LeaveGrantResponse</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -4926,12 +5160,12 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>単一応答 {leaveType}</t>
+          <t>付与 1 行分の応答（POST/PUT の戻り・GET の要素）</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -4939,7 +5173,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeListResponse</t>
+          <t>LeaveGrantRow</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -4954,12 +5188,12 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>一覧応答 {leaveTypes[]}</t>
+          <t>findGrantRows の戻り型（内部用）</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -4967,7 +5201,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeOptionListResponse</t>
+          <t>LeaveTypeDetailResponse</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -4982,12 +5216,12 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>一覧応答 {leaveTypes[]}</t>
+          <t>単一応答 {leaveType}</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>ONL-021</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -4995,7 +5229,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeOptionResponse</t>
+          <t>LeaveTypeListResponse</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -5010,12 +5244,12 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>プルダウン用 1 件（5 項目）。ONL-015 の LeaveTypeResponse（管理者用 7 項目）とは別</t>
+          <t>一覧応答 {leaveTypes[]}</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>ONL-021</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -5023,7 +5257,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeRequest</t>
+          <t>LeaveTypeOptionListResponse</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -5038,12 +5272,12 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>登録・変更リクエスト＋入力チェック</t>
+          <t>一覧応答 {leaveTypes[]}</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-021</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -5051,7 +5285,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeResponse</t>
+          <t>LeaveTypeOptionResponse</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -5066,12 +5300,12 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>休暇種別1件の表現</t>
+          <t>プルダウン用 1 件（5 項目）。ONL-015 の LeaveTypeResponse（管理者用 7 項目）とは別</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-021</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -5079,7 +5313,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>LoginRequest</t>
+          <t>LeaveTypeRequest</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -5094,12 +5328,12 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>リクエスト＋入力チェック定義</t>
+          <t>登録・変更リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -5107,7 +5341,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>LoginResponse</t>
+          <t>LeaveTypeResponse</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -5122,12 +5356,12 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>正常応答</t>
+          <t>休暇種別1件の表現</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -5135,7 +5369,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>MonthlyAttendanceResponse</t>
+          <t>LoginRequest</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -5150,12 +5384,12 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
+          <t>リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>ONL-004</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -5163,7 +5397,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>MonthlyReportResponse</t>
+          <t>LoginResponse</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -5178,12 +5412,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>JSON 応答（month / departmentId / rows[]）</t>
+          <t>正常応答（token / userId / name / role / mustChangePassword）</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -5191,7 +5425,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>MonthlyReportRow</t>
+          <t>MonthlyAttendanceResponse</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -5206,24 +5440,20 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>社員 1 行分の集計（ONL-020 と共用）</t>
+          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>ONL-018</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>ONL-020</t>
-        </is>
-      </c>
+          <t>ONL-004</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>NotificationListResponse</t>
+          <t>MonthlyReportResponse</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -5238,12 +5468,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>GET の正常応答（notifications[]）</t>
+          <t>JSON 応答（month / departmentId / rows[]）</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -5251,7 +5481,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>NotificationResponse</t>
+          <t>MonthlyReportRow</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -5266,20 +5496,24 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>通知1件（id, type, message, requestId, createdAt, isRead）。POST の応答にも使用</t>
+          <t>社員 1 行分の集計（ONL-020 と共用）</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="n"/>
+          <t>ONL-018</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>ONL-020</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>PasswordResetRequest</t>
+          <t>NotificationListResponse</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -5294,12 +5528,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>パスワード設定リクエスト＋入力チェック</t>
+          <t>GET の正常応答（notifications[]）</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-019</t>
         </is>
       </c>
       <c r="F52" s="10" t="n"/>
@@ -5307,7 +5541,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PendingApprovalItem</t>
+          <t>NotificationResponse</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -5322,12 +5556,12 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>応答の1行（日時は +09:00 付き ISO 8601 文字列）</t>
+          <t>通知1件（id, type, message, requestId, createdAt, isRead）。POST の応答にも使用</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-019</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -5335,7 +5569,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>PendingApprovalListResponse</t>
+          <t>PasswordResetRequest</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -5350,12 +5584,12 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>正常応答（items）</t>
+          <t>パスワード設定リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -5363,7 +5597,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PendingApprovalRow</t>
+          <t>PendingApprovalItem</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -5378,7 +5612,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>検索結果の1行（LocalDateTime のまま。JPQL コンストラクタ式用）</t>
+          <t>応答の1行（日時は +09:00 付き ISO 8601 文字列）</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -5391,7 +5625,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>RequestDetailResponse / RequestDetail / StepDetail</t>
+          <t>PendingApprovalListResponse</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -5406,12 +5640,12 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>正常応答（申請内容・承認履歴・申請者残日数）</t>
+          <t>正常応答（items）</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -5419,7 +5653,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>RequestListResponse</t>
+          <t>PendingApprovalRow</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -5434,12 +5668,12 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>正常応答 {requests: [...]}</t>
+          <t>検索結果の1行（LocalDateTime のまま。JPQL コンストラクタ式用）</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>ONL-006</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -5447,7 +5681,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>RequestSummary</t>
+          <t>RequestDetailResponse / RequestDetail / StepDetail</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -5462,12 +5696,12 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>一覧の1行分</t>
+          <t>正常応答（申請内容・承認履歴・申請者残日数）</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>ONL-006</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -5475,7 +5709,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>SubmitRequestResponse</t>
+          <t>RequestListResponse</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -5490,12 +5724,12 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>正常応答 {requestId, status}</t>
+          <t>正常応答 {requests: [...]}</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-006</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -5503,7 +5737,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>SubordinateSummaryResponse</t>
+          <t>RequestSummary</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -5518,12 +5752,12 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>応答（month / rows[]）</t>
+          <t>一覧の1行分</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-006</t>
         </is>
       </c>
       <c r="F60" s="10" t="n"/>
@@ -5531,7 +5765,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>UserCreateRequest</t>
+          <t>SubmitRequestResponse</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -5546,12 +5780,12 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>登録リクエスト＋入力チェック</t>
+          <t>正常応答 {requestId, status}</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -5559,7 +5793,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>UserDetailResponse</t>
+          <t>SubordinateSummaryResponse</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -5574,12 +5808,12 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>単一応答 {user}</t>
+          <t>応答（month / rows[]）</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -5587,7 +5821,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>UserListResponse</t>
+          <t>UserCreateRequest</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -5602,7 +5836,7 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>一覧応答 {users[], total}</t>
+          <t>登録リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -5615,7 +5849,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>UserResponse</t>
+          <t>UserDetailResponse</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -5630,7 +5864,7 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>ユーザー1件の表現（password_hash は含めない）</t>
+          <t>単一応答 {user}</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -5643,7 +5877,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>UserUpdateRequest</t>
+          <t>UserListResponse</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -5658,7 +5892,7 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>変更・無効化リクエスト＋入力チェック</t>
+          <t>一覧応答 {users[], total}</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -5671,7 +5905,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>WithdrawResponse</t>
+          <t>UserResponse</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -5686,12 +5920,12 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>正常応答 {status}</t>
+          <t>ユーザー1件の表現（password_hash は含めない）</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="F66" s="10" t="n"/>
@@ -5699,27 +5933,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>ApprovalStep</t>
+          <t>UserUpdateRequest</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>dto</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>DTO(record)</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>approval_steps テーブルのマッピング</t>
+          <t>変更・無効化リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="F67" s="10" t="n"/>
@@ -5727,39 +5961,35 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>ApprovalStep / Request / User</t>
+          <t>WithdrawResponse</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>dto</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>DTO(record)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>各テーブルのマッピング（新規作成しない）。定数 RequestStatus / StepStatus（ONL-005）も使用</t>
+          <t>正常応答 {status}</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>ONL-011, ONL-012</t>
-        </is>
-      </c>
+          <t>ONL-008</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>ApprovalStep / Request / User / AttendanceRecord</t>
+          <t>ApprovalStep</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -5774,24 +6004,20 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>各テーブルのマッピング（本処理では新規作成しない）</t>
+          <t>approval_steps テーブルのマッピング</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>ApprovalStep / Request / User / Department</t>
+          <t>ApprovalStep / Request / User</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -5806,7 +6032,7 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>結合検索の対象（本処理では新規作成しない）</t>
+          <t>各テーブルのマッピング（新規作成しない）。定数 RequestStatus / StepStatus（ONL-005）も使用</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -5816,14 +6042,14 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-011, ONL-012</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>AttendanceRecord</t>
+          <t>ApprovalStep / Request / User / AttendanceRecord</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -5838,24 +6064,24 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>attendance_records テーブルのマッピング</t>
+          <t>各テーブルのマッピング（本処理では新規作成しない）</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>ONL-003, ONL-004</t>
+          <t>ONL-010</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>ApprovalStep / Request / User / Department</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -5870,24 +6096,24 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>departments のマッピング</t>
+          <t>結合検索の対象（本処理では新規作成しない）</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-009</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>AttendanceRecord</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -5902,24 +6128,24 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>holidays テーブルのマッピング</t>
+          <t>attendance_records テーブルのマッピング</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>ONL-003, ONL-004</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>LeaveBalance</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -5934,24 +6160,24 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>leave_balances テーブルのマッピング</t>
+          <t>departments のマッピング</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>ONL-013, ONL-017</t>
+          <t>ONL-014</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>LeaveType</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -5966,7 +6192,7 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>leave_types テーブルのマッピング</t>
+          <t>holidays テーブルのマッピング</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
@@ -5976,14 +6202,14 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>ONL-013, ONL-015, ONL-021</t>
+          <t>ONL-016</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>LeaveBalance</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -5998,7 +6224,7 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>notifications テーブルのマッピング（type・request_id を含む。ONL-005 が定義）</t>
+          <t>leave_balances テーブルのマッピング</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -6008,14 +6234,14 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-013, ONL-017</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>NotificationType</t>
+          <t>LeaveType</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -6025,12 +6251,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>定数クラス</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>通知種別（REQUEST_SUBMITTED ほか 7 値。KF-BD-005）</t>
+          <t>leave_types テーブルのマッピング</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
@@ -6040,14 +6266,14 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>ONL-008, ONL-010, ONL-011, ONL-012, ONL-017, ONL-019</t>
+          <t>ONL-013, ONL-015, ONL-021</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -6062,7 +6288,7 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>requests テーブルのマッピング</t>
+          <t>notifications テーブルのマッピング（type・request_id を含む。ONL-005 が定義）</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
@@ -6072,14 +6298,14 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>ONL-008, ONL-013</t>
+          <t>ONL-019</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Request / ApprovalStep / User / LeaveType</t>
+          <t>NotificationType</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -6089,29 +6315,29 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>定数クラス</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>各テーブルのマッピング</t>
+          <t>通知種別（REQUEST_SUBMITTED ほか 7 値。KF-BD-005）</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-008, ONL-010, ONL-011, ONL-012, ONL-017, ONL-019</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Request / LeaveType</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -6126,24 +6352,24 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>requests / leave_types のマッピング</t>
+          <t>requests テーブルのマッピング</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>ONL-006</t>
+          <t>ONL-008, ONL-013</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>Request / ApprovalStep / User / LeaveType</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -6153,12 +6379,12 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>定数クラス</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>status 値の検証（ALL）。WITHDRAWABLE（ONL-008）、SUBMITTABLE = DRAFT / RETURNED（ONL-022）</t>
+          <t>各テーブルのマッピング</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -6168,14 +6394,14 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>ONL-006, ONL-008, ONL-022</t>
+          <t>ONL-007</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>RequestType / RequestStatus / LeaveUnit / StepStatus</t>
+          <t>Request / LeaveType</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -6185,25 +6411,29 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>定数クラス</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>KF-BD-005 のコード値（String 定数）</t>
+          <t>requests / leave_types のマッピング</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="n"/>
+          <t>ONL-001 実装済</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>ONL-006</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>RequestType / RequestStatus / StepStatus</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -6218,7 +6448,7 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>KF-BD-005 のコード値（String 定数）。本処理も同じ定数を使う</t>
+          <t>status 値の検証（ALL）。WITHDRAWABLE（ONL-008）、SUBMITTABLE = DRAFT / RETURNED（ONL-022）</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -6228,14 +6458,14 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-006, ONL-008, ONL-022</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>RequestType / RequestStatus / LeaveUnit / StepStatus</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -6245,29 +6475,25 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>定数クラス</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>users テーブルのマッピング</t>
+          <t>KF-BD-005 のコード値（String 定数）</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>ONL-005, ONL-013, ONL-014, ONL-018, ONL-020</t>
-        </is>
-      </c>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>User / LeaveType</t>
+          <t>RequestType / RequestStatus / StepStatus</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -6277,12 +6503,12 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>定数クラス</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>users / leave_types のマッピング</t>
+          <t>KF-BD-005 のコード値（String 定数）。本処理も同じ定数を使う</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
@@ -6292,29 +6518,29 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-010</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>BusinessException</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>業務エラー（コード・HTTPステータス保持）</t>
+          <t>users テーブルのマッピング（failedLoginCount / lockedUntil / mustChangePassword / passwordChangedAt を含む）</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
@@ -6324,29 +6550,29 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>ONL-002, ONL-013, ONL-014, ONL-015, ONL-016</t>
+          <t>ONL-005, ONL-013, ONL-014, ONL-018, ONL-020, ONL-023</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>BusinessException / ErrorResponse</t>
+          <t>User / LeaveType</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>共通部品</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>業務エラー・共通エラー応答</t>
+          <t>users / leave_types のマッピング</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -6356,14 +6582,14 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-017</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>BusinessException / GlobalExceptionHandler</t>
+          <t>BusinessException</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -6373,29 +6599,29 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Exception / ControllerAdvice</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>業務エラーの保持と共通エラー応答への変換</t>
+          <t>業務エラー（コード・HTTPステータス保持）</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>ONL-003, ONL-004, ONL-009, ONL-010, ONL-011, ONL-012, ONL-017, ONL-018, ONL-019, ONL-020</t>
+          <t>ONL-002, ONL-013, ONL-014, ONL-015, ONL-016, ONL-023</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>BusinessException / GlobalExceptionHandler / ErrorResponse</t>
+          <t>BusinessException / ErrorResponse</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -6420,14 +6646,14 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>ONL-005, ONL-006, ONL-008</t>
+          <t>ONL-007</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler</t>
+          <t>BusinessException / GlobalExceptionHandler</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -6437,93 +6663,93 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>ControllerAdvice</t>
+          <t>Exception / ControllerAdvice</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>例外→共通エラー応答への変換（handleAccessDenied / handleTypeMismatch を ONL-001 で定義）</t>
+          <t>業務エラーの保持と共通エラー応答への変換</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>ONL-002, ONL-007, ONL-014, ONL-015, ONL-016, ONL-021</t>
+          <t>ONL-003, ONL-004, ONL-009, ONL-010, ONL-011, ONL-012, ONL-017, ONL-018, ONL-019, ONL-020</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>ApprovalStepRepository</t>
+          <t>BusinessException / GlobalExceptionHandler / ErrorResponse</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>repository</t>
+          <t>exception</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>共通部品</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>approval_steps の登録・検索（ONL-022 が deleteByRequestId を追加）</t>
+          <t>業務エラー・共通エラー応答</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>ONL-009, ONL-010, ONL-011, ONL-012, ONL-022</t>
+          <t>ONL-005, ONL-006, ONL-008</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>AttendanceRecordRepository</t>
+          <t>GlobalExceptionHandler</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>repository</t>
+          <t>exception</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>ControllerAdvice</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>attendance_records の検索（行ロック付き）・保存</t>
+          <t>例外→共通エラー応答への変換（handleAccessDenied / handleTypeMismatch を ONL-001 で定義）</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>ONL-003, ONL-004, ONL-010</t>
+          <t>ONL-002, ONL-007, ONL-014, ONL-015, ONL-016, ONL-021, ONL-023</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>DepartmentRepository</t>
+          <t>ApprovalStepRepository</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -6538,24 +6764,24 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>部署名の取得（findById）</t>
+          <t>approval_steps の登録・検索（ONL-022 が deleteByRequestId を追加）</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-009, ONL-010, ONL-011, ONL-012, ONL-022</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>HolidayRepository</t>
+          <t>AttendanceRecordRepository</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -6570,24 +6796,24 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>holidays の期間検索（findByHolidayDateBetweenOrderByHolidayDate）・存在確認</t>
+          <t>attendance_records の検索（行ロック付き）・保存</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>ONL-003, ONL-004, ONL-010</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>LeaveBalanceRepository</t>
+          <t>DepartmentRepository</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -6602,24 +6828,24 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>leave_balances の残日数集計</t>
+          <t>部署名の取得（findById）</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>ONL-013, ONL-017</t>
+          <t>ONL-014</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>LeaveTypeRepository</t>
+          <t>HolidayRepository</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -6634,7 +6860,7 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>leave_types の ID 検索（JpaRepository#findById を使用）</t>
+          <t>holidays の期間検索（findByHolidayDateBetweenOrderByHolidayDate）・存在確認</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -6644,14 +6870,14 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>ONL-006, ONL-013, ONL-015, ONL-017, ONL-021</t>
+          <t>ONL-016</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>NotificationRepository</t>
+          <t>LeaveBalanceRepository</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -6666,24 +6892,24 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>通知の検索・既読化 UPDATE（本処理で3メソッドを追加）</t>
+          <t>leave_balances の残日数集計</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-013, ONL-017</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>NotificationRepository</t>
+          <t>LeaveTypeRepository</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -6698,7 +6924,7 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>通知の登録・検索・既読化 UPDATE・existsMonthly</t>
+          <t>leave_types の ID 検索（JpaRepository#findById を使用）</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -6708,14 +6934,14 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-006, ONL-013, ONL-015, ONL-017, ONL-021</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>ReportRepository</t>
+          <t>NotificationRepository</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -6730,24 +6956,24 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>月次集計の集計 SQL（GROUP BY を 1 本で発行）</t>
+          <t>通知の検索・既読化 UPDATE（本処理で3メソッドを追加）</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-019</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>RequestRepository</t>
+          <t>NotificationRepository</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -6762,7 +6988,7 @@
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>requests の検索・登録・行ロック</t>
+          <t>通知の登録・検索・既読化 UPDATE・existsMonthly</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
@@ -6772,14 +6998,14 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>ONL-006, ONL-008, ONL-010, ONL-011, ONL-012, ONL-013, ONL-022</t>
+          <t>ONL-019</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>RequestRepository / ApprovalStepRepository</t>
+          <t>ReportRepository</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -6794,24 +7020,24 @@
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>申請・承認ステップの取得（findById / findByRequestIdOrderByStepNo）</t>
+          <t>月次集計の集計 SQL（GROUP BY を 1 本で発行）</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>ONL-001 実装済</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-020</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>UserRepository</t>
+          <t>RequestRepository</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -6826,24 +7052,24 @@
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>users のメール検索</t>
+          <t>requests の検索・登録・行ロック</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>ONL-005, ONL-009, ONL-010, ONL-011, ONL-012, ONL-013, ONL-014, ONL-017, ONL-022</t>
+          <t>ONL-006, ONL-008, ONL-010, ONL-011, ONL-012, ONL-013, ONL-022</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>UserRepository / LeaveTypeRepository</t>
+          <t>RequestRepository / ApprovalStepRepository</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -6858,7 +7084,7 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>氏名・ロール・種別名の取得（findById / findAllById）</t>
+          <t>申請・承認ステップの取得（findById / findByRequestIdOrderByStepNo）</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
@@ -6875,22 +7101,22 @@
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>JwtService</t>
+          <t>UserRepository</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>JWT 発行</t>
+          <t>users のメール検索 findByEmail、ID 検索 findById（標準）</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
@@ -6898,44 +7124,48 @@
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="F104" s="10" t="n"/>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>ONL-005, ONL-009, ONL-010, ONL-011, ONL-012, ONL-013, ONL-014, ONL-017, ONL-022, ONL-023</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler</t>
+          <t>UserRepository / LeaveTypeRepository</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す（AccessDeniedHandler）</t>
+          <t>氏名・ロール・種別名の取得（findById / findAllById）</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-001 実装済</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>全認証必須 API</t>
+          <t>ONL-007</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
+          <t>JwtService</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -6945,12 +7175,12 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>トークンなし・不正・期限切れを 401 / E-001 の JSON で返す（AuthenticationEntryPoint）</t>
+          <t>JWT 発行（HS256、有効2時間）</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -6958,11 +7188,7 @@
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>全認証必須 API</t>
-        </is>
-      </c>
+      <c r="F106" s="10" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -7110,7 +7336,7 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>ログイン業務ロジック（ONL-001 本体）</t>
+          <t>ログイン業務ロジック（ONL-001 本体。ロック判定・失敗回数管理を含む）。changePassword / validatePolicy は ONL-023 で追加</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
@@ -7118,7 +7344,11 @@
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="F111" s="10" t="n"/>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -7358,12 +7588,12 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>メールアドレスの正規化 trim().toLowerCase(Locale.ROOT)。保存時・検索時に使用</t>
+          <t>【未実装・設計案】メールアドレスの正規化 trim().toLowerCase(Locale.ROOT)。現行は AuthService#login 内で直接実行（ONL-014 実装時にクラス化）</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-001（未実装）</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
@@ -7377,13 +7607,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7422,7 +7652,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>@EnableMethodSecurity を付与し、exceptionHandling / oauth2ResourceServer に RestAuthenticationEntryPoint・RestAccessDeniedHandler を設定する</t>
+          <t>@EnableMethodSecurity を付与し、oauth2ResourceServer に authenticationEntryPoint（401 / E-001）・accessDeniedHandler（403 / E-010）をラムダで設定する（401 / 403 は実装済み。@EnableMethodSecurity は @PreAuthorize を使う API の実装時）</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -7439,12 +7669,12 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint（新規）</t>
+          <t>SecurityConfig#authenticationEntryPoint（実装済み）</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>トークンなし・不正・期限切れを 401 / E-001 の JSON（ErrorResponse）で返す</t>
+          <t>トークンなし・不正・期限切れを 401 / E-001 の JSON（ErrorResponse）で返す。文言『認証が必要です。再度ログインしてください。』</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -7461,7 +7691,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler（新規）</t>
+          <t>SecurityConfig#accessDeniedHandler（実装済み）</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -7519,12 +7749,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>EmailNormalizer（新規）</t>
+          <t>EmailNormalizer（新規・未実装。ONL-014 実装時に共通化）</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>trim().toLowerCase(Locale.ROOT)。保存時・検索時に使用</t>
+          <t>trim().toLowerCase(Locale.ROOT)。保存時・検索時に使用。現行コードでは AuthService#login 内で直接実行（クラス化は ONL-014 実装時）</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -7596,7 +7826,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>確定（schema.sql に反映済み）。UPDATE 文の SET に updated_at を含めない</t>
+          <t>確定（V1__init_schema.sql に反映済み）。UPDATE 文の SET に updated_at を含めない</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7848,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>確定（schema.sql に反映済み）。旧『SCR-106 で代替』は廃止</t>
+          <t>確定（V1__init_schema.sql に反映済み）。旧『SCR-106 で代替』は廃止</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7870,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>確定（schema.sql に反映済み）</t>
+          <t>確定（V1__init_schema.sql に反映済み）</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7926,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>保存時・検索時とも trim().toLowerCase(Locale.ROOT) で正規化（大文字小文字を区別しない）</t>
+          <t>保存時・検索時とも trim().toLowerCase(Locale.ROOT) で正規化（大文字小文字を区別しない）。ログインは実装済み（AuthService#login 内）</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -7706,7 +7936,95 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>既存データは UPDATE users SET email = LOWER(TRIM(email)) で一度正規化する必要がある</t>
+          <t>旧データは UPDATE users SET email = LOWER(TRIM(email)) で一度正規化する必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>users（4 列追加）</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>failed_login_count / locked_until / must_change_password / password_changed_at を追加（V1__init_schema.sql）</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ONL-001, ONL-023</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>開発 DB が旧 schema.sql 由来の場合は backend/db/reset-dev.sql で作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>DB 変更管理（Flyway）</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（db/migration/V1__init_schema.sql）に移行。ddl-auto=validate。V1 は変更しない（変更は V2 以降を追加）</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>全処理</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>KF-DD-006 参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password（API-023）</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>パスワード変更を新設（AuthController#changePassword / AuthService#changePassword / validatePolicy）</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>KF-BD-011 に追加済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer（新規）</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>本番の初期管理者1名を作成（users が空かつ設定が揃うときのみ）</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>環境変数 BOOTSTRAP_ADMIN_* で指定（KF-DD-006）</t>
         </is>
       </c>
     </row>
@@ -7721,7 +8039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7798,7 +8116,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>users: R</t>
+          <t>users: R/U</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
@@ -8581,6 +8899,43 @@
       <c r="G23" s="10" t="inlineStr">
         <is>
           <t>KF-DD-ONL-022_申請提出_オンライン詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>API-023</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>users: R/U</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -8594,9 +8949,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8619,7 +8974,7 @@
       <c r="E1" s="12" t="n"/>
       <c r="F1" s="13" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>処理ID/名</t>
@@ -8635,7 +8990,7 @@
       <c r="E2" s="12" t="n"/>
       <c r="F2" s="13" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>機能ID</t>
@@ -8643,7 +8998,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>F-01 ログイン</t>
+          <t>F-01 ログイン、F-13 アカウントロック</t>
         </is>
       </c>
       <c r="C3" s="12" t="n"/>
@@ -8651,7 +9006,7 @@
       <c r="E3" s="12" t="n"/>
       <c r="F3" s="13" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>画面 / API</t>
@@ -8667,7 +9022,7 @@
       <c r="E4" s="12" t="n"/>
       <c r="F4" s="13" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>認可</t>
@@ -8683,7 +9038,7 @@
       <c r="E5" s="12" t="n"/>
       <c r="F5" s="13" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>処理概要</t>
@@ -8691,7 +9046,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードで本人確認を行い、成功時に認証トークン（JWT）を発行する。</t>
+          <t>メールアドレスとパスワードで本人確認を行い、成功時に認証トークン（JWT、有効 2 時間）を発行する。連続 5 回のパスワード誤りでアカウントを 30 分ロックする。初期パスワードの利用者には mustChangePassword=true を返し、パスワード変更（ONL-023）へ誘導する。</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
@@ -8699,7 +9054,7 @@
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="13" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>使用テーブル</t>
@@ -8707,7 +9062,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>users: R</t>
+          <t>users: R/U（失敗回数・ロック日時の更新）</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
@@ -8715,7 +9070,7 @@
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="13" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>トランザクション</t>
@@ -8723,7 +9078,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>読み取り専用（@Transactional(readOnly = true)）。データ更新なし。</t>
+          <t>更新あり。@Transactional(noRollbackFor = BusinessException.class)。パスワード不一致で E-001 を投げても、失敗回数・ロック日時の UPDATE はコミットする（既定のままだと失敗回数が保存されずロックが機能しない）。</t>
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
@@ -8731,7 +9086,7 @@
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="13" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>実装クラス</t>
@@ -8739,7 +9094,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>AuthController#login → AuthService#login → UserRepository#findByEmail / JwtService#issue</t>
+          <t>AuthController#login → AuthService#login → UserRepository#findByEmail / PasswordEncoder#matches / UserRepository#save / JwtService#issue</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -8747,7 +9102,6 @@
       <c r="E9" s="12" t="n"/>
       <c r="F9" s="13" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -8760,7 +9114,7 @@
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="13" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>項目名</t>
@@ -8792,7 +9146,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="84" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>email</t>
@@ -8821,11 +9175,12 @@
       <c r="F13" s="10" t="inlineStr">
         <is>
           <t>未入力（空白のみ含む）: E-002「メールアドレスは必須入力です。」
-256文字以上: E-002「メールアドレスは255文字以内で入力してください。」</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+256文字以上: E-002「メールアドレスは255文字以内で入力してください。」
+前後の空白除去・小文字化はサーバーで実施（照合前に正規化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43.5" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>password</t>
@@ -8853,11 +9208,11 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>未入力（空白のみ含む）: E-002「パスワードは必須入力です。」</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>未入力（空白のみ含む）: E-002「パスワードは必須入力です。」（ポリシー検査はログインでは行わない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>（本文全体）</t>
@@ -8889,7 +9244,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -8902,7 +9256,7 @@
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="13" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>No.</t>
@@ -8930,7 +9284,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>1</t>
@@ -8958,7 +9312,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="43.5" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2</t>
@@ -8971,8 +9325,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>users から email が完全一致するレコードを1件取得
-（SELECT * FROM users WHERE email = ?）</t>
+          <t>email を trim().toLowerCase(Locale.ROOT) で正規化し、users から完全一致で1件取得</t>
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
@@ -8987,7 +9340,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>3</t>
@@ -9000,7 +9353,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>users.status = 'ACTIVE' であること</t>
+          <t>users.status = 'ACTIVE' であること（失敗回数は加算しない）</t>
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
@@ -9015,7 +9368,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="57" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>4</t>
@@ -9023,27 +9376,27 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>パスワード照合</t>
+          <t>ロック確認</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>入力 password と users.password_hash を BCrypt で照合（PasswordEncoder#matches）</t>
+          <t>locked_until が現在日時（JST）より後ならロック中。正しいパスワードでも拒否する（パスワード照合より前に判定）</t>
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>不一致</t>
+          <t>ロック中</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>E-001  HTTP 401</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>E-017  HTTP 423</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>5</t>
@@ -9051,27 +9404,27 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>トークン発行</t>
+          <t>パスワード照合</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>JWT を生成する（「5. トークン仕様」参照）</t>
+          <t>入力 password と users.password_hash を BCrypt で照合（PasswordEncoder#matches）。不一致のときは failed_login_count を +1 して保存（5 回目は locked_until = 現在日時 + 30 分、failed_login_count = 0）</t>
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>不一致</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>E-001  HTTP 401（更新はコミットする）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="43.5" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>6</t>
@@ -9079,120 +9432,127 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>レスポンス返却</t>
+          <t>失敗回数リセット</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>「4. 出力項目」を返す</t>
+          <t>failed_login_count ≠ 0 または locked_until ≠ NULL の場合のみ、0 / NULL に更新</t>
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>トークン発行</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>JWT を生成する（「5. トークン仕様」参照）</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>レスポンス返却</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>「4. 出力項目」を返す</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>HTTP 200</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>4. 出力項目（正常時 HTTP 200）</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="13" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>項目名</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>論理名</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>編集内容</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>token</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>認証トークン</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>文字列</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>JWT。以降の API は Authorization: Bearer &lt;token&gt; で送る</t>
-        </is>
-      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="13" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>users.id</t>
+    <row r="29" ht="16.5" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>編集内容</t>
         </is>
       </c>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="13" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="16.5" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>氏名</t>
+          <t>認証トークン</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -9202,361 +9562,500 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>users.name</t>
+          <t>JWT。以降の API は Authorization: Bearer &lt;token&gt; で送る</t>
         </is>
       </c>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="13" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="16.5" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>ロール</t>
+          <t>ユーザーID</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>文字列</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>users.role（EMPLOYEE / MANAGER / ADMIN）</t>
+          <t>users.id</t>
         </is>
       </c>
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="13" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>5. トークン仕様（JWT）</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>文字列</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>users.name</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>ロール</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>文字列</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>users.role（EMPLOYEE / MANAGER / ADMIN）</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="13" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>署名方式</t>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>mustChangePassword</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>HS256（共通鍵）。鍵は設定値 kintaiflow.jwt.secret（Git管理外の application-local.properties）</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
+          <t>要パスワード変更</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>真偽値</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>users.must_change_password。true の間、画面は SCR-007（/password）に固定する</t>
+        </is>
+      </c>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="13" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>クレーム</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>iss = kintaiflow／sub = users.id／role = users.role／iat = 発行日時／exp = 発行から8時間後</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="13" t="n"/>
-    </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>有効期間</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>8時間（設定値 kintaiflow.jwt.expiration-hours）。期限切れ後は再ログインが必要</t>
-        </is>
-      </c>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>5. トークン仕様（JWT）</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="12" t="n"/>
       <c r="E36" s="12" t="n"/>
       <c r="F36" s="13" t="n"/>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>6. エラー一覧</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n"/>
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>署名方式</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>HS256（共通鍵）。鍵は設定値 kintaiflow.jwt.secret（Git 管理外。環境変数／.env から注入）</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>クレーム</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>iss = kintaiflow／sub = users.id／role = users.role／iat = 発行日時／exp = 発行から2時間後</t>
+        </is>
+      </c>
       <c r="C38" s="12" t="n"/>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="12" t="n"/>
       <c r="F38" s="13" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>有効期間</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2時間（設定値 kintaiflow.jwt.expiration-hours）。期限切れ後は再ログインが必要。トークンの失効（ログアウト無効化）は未実装</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>6. エラー一覧</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="13" t="n"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>コード</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>メッセージ</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>発生条件</t>
         </is>
       </c>
-      <c r="F39" s="13" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="F42" s="13" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>E-001</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>401</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>メールアドレスまたはパスワードが正しくありません。</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>処理フロー 2・3・4 のいずれか</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>処理フロー 2・3・5 のいずれか。トークンなし・不正・期限切れ（認証必須 API）も 401 / E-001</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+    </row>
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>E-017</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>アカウントがロックされています。しばらくしてから再度お試しください。</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>処理フロー 4（ロック中）</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>E-010</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>この操作を行う権限がありません。</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>フィルタ段階の権限不足（AccessDeniedHandler。JSON で返す）</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>E-002</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>項目ごとのメッセージ（2. 参照）</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>入力チェック不正／JSON不正</t>
         </is>
       </c>
-      <c r="F41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="F46" s="13" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>E-012</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>システムエラー（メッセージ一覧参照）</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>予期しない例外（ログに記録）</t>
         </is>
       </c>
-      <c r="F42" s="13" t="n"/>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="F47" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>7. 設計上の留意点</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>情報漏えい防止</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>「ユーザー不存在」「無効ユーザー」「パスワード違い」は同一の E-001 を返す。どれが原因かを呼び出し側に知らせない（メールアドレスの登録有無の推測を防ぐ）。</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>秘密情報の扱い</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>password_hash はレスポンスに含めない。パスワード・トークンをログに出力しない。</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="13" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>メールアドレスの大小文字</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>完全一致で検索する（大文字小文字を区別）。登録時の表記どおりに入力する。</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="13" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>対象外（将来検討）</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>連続失敗によるアカウントロック／最終ログイン日時の記録／トークン失効（ログアウト）。必要になった時点で本書を改訂する。</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="13" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>開発用データ</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>開発環境のみ、users が空の起動時に DevDataInitializer が4アカウント（ADMIN/MANAGER/EMPLOYEE×2）を投入する。本番では使用しない。</t>
-        </is>
-      </c>
+      <c r="B49" s="12" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="n"/>
       <c r="E49" s="12" t="n"/>
       <c r="F49" s="13" t="n"/>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>8. 処理フロー図</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n"/>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>情報漏えい防止</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>「ユーザー不存在」「無効ユーザー」「パスワード違い」は同一の E-001 を返す。どれが原因かを呼び出し側に知らせない。ロック中だけは E-017（423）で区別する（ロック状態の通知を優先）。</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>秘密情報の扱い</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>password_hash はレスポンスに含めない。パスワード・トークンをログに出力しない。初期管理者作成時のログにはメールアドレスのみを出す。</t>
+        </is>
+      </c>
       <c r="C51" s="12" t="n"/>
       <c r="D51" s="12" t="n"/>
       <c r="E51" s="12" t="n"/>
       <c r="F51" s="13" t="n"/>
     </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>メールアドレスの大小文字</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>入力は前後の空白除去・小文字化して検索する（大文字小文字を区別しない）。EmailNormalizer クラスは未実装で、現行は AuthService#login 内で直接実行（ONL-014 実装時に共通化）。</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>ロックの仕様</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>ロック中の試行は失敗回数に加算しない。ロックは 30 分で自動解除。管理者による手動解除は未実装。</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="12" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="13" t="n"/>
+    </row>
+    <row r="54" ht="16.5" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>既知の課題</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>mustChangePassword=true のユーザーでもサーバー側は他 API を拒否しない（画面のルーターガードのみ）。トークン失効・監査ログも未実装。</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>開発用データ</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>開発環境のみ、users が空の起動時に DevDataInitializer が架空ユーザー 100 名（ADMIN / MANAGER / EMPLOYEE）を投入する（seed-password 設定時のみ）。本番では BootstrapAdminInitializer が初期管理者 1 名のみを作成する。</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n"/>
+      <c r="D55" s="12" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>8. 処理フロー図</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="52">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="E43:F43"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="E42:F42"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C44:D44"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C40:D40"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="E45:F45"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E41:F41"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -9730,7 +10229,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -9949,7 +10447,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
@@ -10120,7 +10617,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -10351,7 +10847,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
@@ -10510,7 +11005,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
